--- a/src/model/prompt_tests/Prompt_Chaining_Test.xlsx
+++ b/src/model/prompt_tests/Prompt_Chaining_Test.xlsx
@@ -1,69 +1,95 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bruce/Desktop/APCOMP 215/AC215_888/src/model/prompt_tests/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB2FD54-3464-7144-B884-C5A47123070B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="1300" yWindow="10980" windowWidth="28100" windowHeight="16880" xr2:uid="{60DE08AB-C148-5C4E-A3EA-40F02C48914F}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>A patient with tuberculosis receiving isoniazid therapy under directly observed treatment developed acute hepatitis after 3 months. Liver enzymes were monitored monthly and were normal until the week prior. The medication was discontinued immediately, but the patient developed hepatic failure requiring transfer for transplant evaluation.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A patient was admitted to the critical care unit with congestive heart failure and later has a new complaint of chest pain persisting over several hours. Tylenol is administered but does not decrease the patient’s pain scale rating. The Resident orders a laboratory work-up. An EKG shows that the patient is experiencing an acute ST-elevation myocardial infarction. The attending cardiologist is called, but does not respond to multiple pages. The nurse does not escalate the patient’s emergent condition to other physicians or the rapid response team. The patient continues to decompensate, codes and expires.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>An anesthesiologist prepared syringes containing lidocaine and epinephrine in similar clear syringes without labels. Before administration, the nurse anesthetist questioned which syringe contained which medication. The anesthesiologist realized the mix-up risk, labeled both syringes correctly, and no wrong drug was given.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A 65-year-old man with COPD was receiving long-term IV antibiotics through a PICC line. The dressing was not changed for over 10 days, and the line was accessed multiple times without proper aseptic technique. He developed chills, hypotension, and positive blood cultures for MRSA. Despite antibiotics and line removal, he developed endocarditis and died 2 weeks later.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A 50-year-old man presented to the emergency department with mild chest discomfort. An ECG was obtained and automatically interpreted as “possible ischemia.” The attending physician did not review the tracing before discharge, assuming the pain was musculoskeletal. The patient was called back the next morning after radiology over-read confirmed minor ST changes. He was asymptomatic and later diagnosed with stable angina, started on medication.</t>
+  </si>
+  <si>
+    <t>A patient was receiving care in an OB Clinic. This patient had a history of insulin dependent gestational diabetes. Although the clinic did instruct the patient in how to care for the problem, she was known to have some behavioral health and social issues and was inconsistent in self-care and didn’t always keep her visits. They discussed options to more safely care for this patient but hadn’t implemented a plan of care. Ultimately the patient delivered the infant via c section, but there was unfortunately a fetal demise.</t>
+  </si>
   <si>
     <t>Brief Factual Description</t>
-  </si>
-  <si>
-    <t>HPI Label</t>
-  </si>
-  <si>
-    <t>A patient was admitted to the critical care unit with congestive heart failure and later has a new complaint of chest pain persisting over several hours. Tylenol is administered but does not decrease the patient’s pain scale rating. The Resident orders a laboratory work-up. An EKG shows that the patient is experiencing an acute ST-elevation myocardial infarction. The attending cardiologist is called, but does not respond to multiple pages. The nurse does not escalate the patient’s emergent condition to other physicians or the rapid response team. The patient continues to decompensate, codes and expires.</t>
-  </si>
-  <si>
-    <t>SSE</t>
-  </si>
-  <si>
-    <t>A patient was being treated in the Cardiac Progressive Care Unit and had a heparin lock in place. As part of the routine hep-lock care, the nurse administered what she thought was the usual hep-lock flush solution from an unlabeled syringe she previously placed at the bedside. However, the syringe actually contained Cardizem, which she administered to the patient. The patient experienced an immediate hypotensive reaction, which quickly resolved without further incident.</t>
-  </si>
-  <si>
-    <t>PSE</t>
-  </si>
-  <si>
-    <t>A physician was providing care via the TeleHealth service for a Primary Care Clinic. A patient with a history of atrial fibrillation needed a new prescription for coumadin. Blood work had been obtained and after talking with the patient, the physician ordered the new prescription dose electronically. However, he inadvertently ordered a much higher does than intended. It wasn’t high enough for the EHR alert to fire. The Pharmacy Tech prepared the medication for the patient to pick up. When the pharmacist in the clinic reviewed the work the Tech had done, he thought the dose seemed much higher than the patient (who he was familiar with) had originally taken and checked the lab results. Realizing the possibility of an error he contacted the physician who was able to correct the error before the medication was dispensed.</t>
-  </si>
-  <si>
-    <t>NME</t>
-  </si>
-  <si>
-    <t>A healthy Gravida 2 Para1 40-week gestation mother presents in active labor requiring routine monitoring according to Labor &amp; Delivery protocols. Labor progresses to delivery of a healthy 6-pound infant with Apgar scores of 10 and 10. Within 2 minutes post-delivery, the mother, who is still being monitored, begins to develop extreme respiratory distress and signs of disseminated intravascular clotting (DIC) syndrome. Despite all emergent efforts to reverse the situation, the mother succumbs to what is later diagnosed as an amniotic fluid embolism.</t>
-  </si>
-  <si>
-    <t>NSE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3">
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <color theme="1"/>
-      <name val="Arial"/>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <name val="DengXian"/>
+      <family val="4"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -71,88 +97,195 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -214,13 +347,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -229,6 +355,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -293,60 +426,83 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{046329A9-2458-8349-B9B0-A482E0490C60}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="25.13"/>
+    <col min="1" max="1" width="34.83203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="17">
       <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="170">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:3" ht="289">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" ht="153">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="187">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
+    <row r="6" spans="1:3" ht="221">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="255">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>